--- a/apps/api/assets/vocabulary/初中/人教版/人教版初中英语九年级全册.xlsx
+++ b/apps/api/assets/vocabulary/初中/人教版/人教版初中英语九年级全册.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D672"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -680,6 +680,16 @@
           <t>look up</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 查找；查阅；探望；看望
@@ -998,6 +1008,16 @@
           <t>be born with</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 天生具有；生而具有；生就</t>
@@ -1123,6 +1143,16 @@
           <t>pay attention to</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 注意
@@ -1157,6 +1187,16 @@
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>connect ... with</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1290,6 +1330,16 @@
           <t>Annie</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
           <t>n. 安妮（女子名）</t>
@@ -1300,6 +1350,16 @@
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Alexander Graham Bell</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2136,6 +2196,16 @@
           <t>Chiang Mai</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【旅】清迈
@@ -2149,6 +2219,16 @@
           <t>Water Festival</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -2161,6 +2241,16 @@
           <t>Mid-Autumn Festival</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
           <t>《英汉医学词典》mid autumn festival
@@ -2174,6 +2264,16 @@
           <t>Mother's Day</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (美国和加拿大的)母亲节
@@ -2187,6 +2287,16 @@
           <t>Father's Day</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 〈美〉父亲节(每年六月的第三个星期日)
@@ -2222,6 +2332,16 @@
           <t>A Christmas Carol</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 圣诞颂歌；小气财神；圣诞欢歌</t>
@@ -2299,6 +2419,16 @@
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Charles Dickens</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -2335,6 +2465,16 @@
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Jacob Marley</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -2719,6 +2859,16 @@
           <t>pardon me</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 对不起；原谅我；请原谅</t>
@@ -3194,6 +3344,16 @@
           <t>parking lot</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 停车场
@@ -3254,6 +3414,16 @@
           <t>Tim</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
           <t>n. 蒂姆（男子名）</t>
@@ -3331,6 +3501,16 @@
       <c r="A133" s="2" t="inlineStr">
         <is>
           <t>from time to time</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -3464,6 +3644,16 @@
       <c r="A139" s="2" t="inlineStr">
         <is>
           <t>deal with</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -3759,6 +3949,16 @@
           <t>in public</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 公然
@@ -3932,6 +4132,16 @@
           <t>boarding school</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 寄宿学校
@@ -3943,6 +4153,16 @@
       <c r="A161" s="2" t="inlineStr">
         <is>
           <t>in person</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -4005,6 +4225,16 @@
           <t>take pride in</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 以…自豪；对…感到满意
@@ -4041,6 +4271,16 @@
           <t>be proud of</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 以…自豪
@@ -4144,6 +4384,16 @@
           <t>Billy</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
           <t>n. 棍棒，警棍；伙伴</t>
@@ -4154,6 +4404,16 @@
       <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Candy</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -4171,6 +4431,16 @@
           <t>Jerry</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
           <t>adj. 偷工减料的；草率的
@@ -4546,6 +4816,16 @@
           <t>be known for</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 公认；闻名；以…著称
@@ -4653,6 +4933,16 @@
           <t>no matter</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 没事儿
@@ -5158,6 +5448,16 @@
           <t>paper cutting</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【艺,文】剪纸(艺术)
@@ -5215,6 +5515,16 @@
       <c r="A219" s="2" t="inlineStr">
         <is>
           <t>fairy tale</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -5367,6 +5677,16 @@
           <t>San Francisco</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 旧金山
@@ -5400,6 +5720,16 @@
       <c r="A228" s="2" t="inlineStr">
         <is>
           <t>Pam</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -5630,6 +5960,16 @@
           <t>have a point</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 有道理；很有道理；有点道理</t>
@@ -5760,6 +6100,16 @@
           <t>by accident</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 偶然 (opp. on purpose)
@@ -5938,6 +6288,16 @@
           <t>take place</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 发生；举行
@@ -5994,6 +6354,16 @@
       <c r="A255" s="2" t="inlineStr">
         <is>
           <t>without doubt</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -6199,6 +6569,16 @@
           <t>all of a sudden</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. “all at once”的变体；突然
@@ -6396,6 +6776,16 @@
           <t>by mistake</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 因错误
@@ -6429,6 +6819,16 @@
       <c r="A275" s="2" t="inlineStr">
         <is>
           <t>the Olympics</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -6490,6 +6890,16 @@
           <t>divide ... into</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 分为
@@ -6526,6 +6936,16 @@
           <t>not only ... but also ...</t>
         </is>
       </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 不仅……而且；不但而且；两个不仅……而且</t>
@@ -6538,6 +6958,16 @@
           <t>look up to</t>
         </is>
       </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 尊敬；另眼看待；向…一举一动看齐
@@ -6662,6 +7092,16 @@
           <t>National Basketball Association</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 全国篮球协会
@@ -6697,6 +7137,16 @@
           <t>China Basketball Association</t>
         </is>
       </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -6729,6 +7179,16 @@
       <c r="A291" s="2" t="inlineStr">
         <is>
           <t>Whitcomb Judson</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
@@ -6768,6 +7228,16 @@
           <t>Thomas Watson</t>
         </is>
       </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -6780,6 +7250,16 @@
           <t>George Crum</t>
         </is>
       </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -6790,6 +7270,16 @@
       <c r="A295" s="2" t="inlineStr">
         <is>
           <t>James Naismith</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
@@ -7135,6 +7625,16 @@
           <t>talk back</t>
         </is>
       </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 回嘴；反复重说；反唇相讥
@@ -7261,6 +7761,16 @@
           <t>keep ... away from</t>
         </is>
       </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
           <t>(使)远离，(使)不接近；(使)不在</t>
@@ -7298,6 +7808,16 @@
           <t>make one's own decision</t>
         </is>
       </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -7376,6 +7896,16 @@
       <c r="A322" s="2" t="inlineStr">
         <is>
           <t>get in the way of</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -7931,6 +8461,16 @@
           <t>run after</t>
         </is>
       </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 〈非正式〉追求；追赶；追捕
@@ -7992,6 +8532,16 @@
           <t>at the same time</t>
         </is>
       </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 同时；另一方面；与此同时
@@ -8051,6 +8601,16 @@
           <t>Great Britain</t>
         </is>
       </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 大不列颠（包括英格兰、苏格兰和威尔士）
@@ -8474,6 +9034,16 @@
           <t>Carla</t>
         </is>
       </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
           <t>abbr. code actuated random load apparatus 代码驱动随机加载装置</t>
@@ -8486,6 +9056,16 @@
           <t>J.K.Rowling</t>
         </is>
       </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -8541,6 +9121,16 @@
       <c r="A375" s="2" t="inlineStr">
         <is>
           <t>Paul Stoker</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -8768,6 +9358,16 @@
           <t>in that case</t>
         </is>
       </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 既然是那样
@@ -8827,6 +9427,16 @@
       <c r="A388" s="2" t="inlineStr">
         <is>
           <t>stick to</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -9009,6 +9619,16 @@
           <t>plenty of</t>
         </is>
       </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 很多的
@@ -9048,6 +9668,16 @@
           <t>shut off</t>
         </is>
       </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 阻断；使隔开
@@ -9081,6 +9711,16 @@
       <c r="A400" s="2" t="inlineStr">
         <is>
           <t>once in a while</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
@@ -9329,6 +9969,16 @@
           <t>in total</t>
         </is>
       </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">adv. 全部；完全
@@ -9460,6 +10110,16 @@
           <t>World War II</t>
         </is>
       </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 第二次世界大战(1939-1945)
@@ -9473,6 +10133,16 @@
           <t>Men in Black</t>
         </is>
       </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 黑衣人；黑超特警组；星际战警</t>
@@ -9485,6 +10155,16 @@
           <t>Kung Fu Panda</t>
         </is>
       </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -9520,6 +10200,16 @@
           <t>March of the Penguins</t>
         </is>
       </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 帝企鹅日记；企鹅宝贝；企鹅的三月</t>
@@ -9532,6 +10222,16 @@
           <t>Spider-Man</t>
         </is>
       </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> [电影]蜘蛛侠</t>
@@ -9544,6 +10244,16 @@
           <t>Carmen</t>
         </is>
       </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
           <t>n. 卡门（女子名）</t>
@@ -9554,6 +10264,16 @@
       <c r="A424" s="2" t="inlineStr">
         <is>
           <t>Dan Dervish</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -9711,6 +10431,16 @@
           <t>drop by</t>
         </is>
       </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 随便访问一下
@@ -9748,6 +10478,16 @@
           <t>after all</t>
         </is>
       </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 毕竟；终究；最后
@@ -9807,6 +10547,16 @@
           <t>get mad</t>
         </is>
       </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 发怒
@@ -9842,6 +10592,16 @@
           <t>make an effort</t>
         </is>
       </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 努力作出
@@ -9875,6 +10635,16 @@
       <c r="A440" s="2" t="inlineStr">
         <is>
           <t>clean ... off</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
@@ -10199,6 +10969,16 @@
           <t>go out of one's way</t>
         </is>
       </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 绕弯儿走；不怕麻烦；特地；故意
@@ -10210,6 +10990,16 @@
       <c r="A455" s="2" t="inlineStr">
         <is>
           <t>make ... feel at home</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -10362,6 +11152,16 @@
           <t>get used to</t>
         </is>
       </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 变得习惯于
@@ -10574,6 +11374,16 @@
           <t>Sato</t>
         </is>
       </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
           <t>abbr. Self-Aligned Thick-Oxide (technique) 自对准厚氧化物层（技术）</t>
@@ -10608,6 +11418,16 @@
           <t>Teresa Lopez</t>
         </is>
       </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10620,6 +11440,16 @@
           <t>Marc LeBlanc</t>
         </is>
       </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -10654,6 +11484,16 @@
       <c r="A477" s="2" t="inlineStr">
         <is>
           <t>would rather</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
@@ -10693,6 +11533,16 @@
           <t>drive sb. crazy</t>
         </is>
       </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 受不了；使…发疯；怒火狂飙</t>
@@ -10705,6 +11555,16 @@
           <t>drive sb. mad</t>
         </is>
       </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
           <t>un. 变疯</t>
@@ -10717,6 +11577,16 @@
           <t>the more ... the more ...</t>
         </is>
       </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
           <t>越...越...</t>
@@ -10751,6 +11621,16 @@
           <t>be friends with sb.</t>
         </is>
       </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 跟…要好
@@ -10762,6 +11642,16 @@
       <c r="A484" s="2" t="inlineStr">
         <is>
           <t>leave out</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
@@ -10902,6 +11792,16 @@
           <t>prime minister</t>
         </is>
       </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 首相；总理
@@ -11082,6 +11982,16 @@
           <t>neither ... nor ...</t>
         </is>
       </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 既不……也不；两者都不；均不</t>
@@ -11136,6 +12046,16 @@
       <c r="A501" s="2" t="inlineStr">
         <is>
           <t>to start with</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
@@ -11294,6 +12214,16 @@
           <t>let ... down</t>
         </is>
       </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 使失望；放下；丢面子
@@ -11357,6 +12287,16 @@
           <t>kick sb. off</t>
         </is>
       </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. (足球)中线开球；开始(某种活动)；死；踢脱(鞋等)
@@ -11370,6 +12310,16 @@
           <t>be hard on sb.</t>
         </is>
       </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 接近
@@ -11449,6 +12399,16 @@
       <c r="A516" s="2" t="inlineStr">
         <is>
           <t>rather than</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
@@ -11514,6 +12474,16 @@
           <t>pull together</t>
         </is>
       </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 通力合作；拼凑
@@ -11708,6 +12678,16 @@
           <t>by the time ...</t>
         </is>
       </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 到…的时候
@@ -11768,6 +12748,16 @@
           <t>give ... a lift</t>
         </is>
       </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 让…搭车；搭便车</t>
@@ -11803,6 +12793,16 @@
       <c r="A533" s="2" t="inlineStr">
         <is>
           <t>in line with</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
@@ -12126,6 +13126,16 @@
           <t>show up</t>
         </is>
       </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 显眼；揭发；嘲笑；露面
@@ -12186,6 +13196,16 @@
       <c r="A550" s="2" t="inlineStr">
         <is>
           <t>by the end of</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
@@ -12272,6 +13292,16 @@
           <t>costume party</t>
         </is>
       </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 化装舞会
@@ -12538,6 +13568,16 @@
           <t>New Zealand</t>
         </is>
       </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. 【国】新西兰
@@ -12593,6 +13633,16 @@
       <c r="A569" s="2" t="inlineStr">
         <is>
           <t>Matt</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D569" s="2" t="inlineStr">
@@ -12631,6 +13681,16 @@
           <t>Carl</t>
         </is>
       </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
           <t>n. 粗野之人；村夫</t>
@@ -12641,6 +13701,16 @@
       <c r="A572" s="2" t="inlineStr">
         <is>
           <t>Orson Welles</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
@@ -13008,6 +14078,16 @@
           <t>be harmful to</t>
         </is>
       </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 对…有害；对…有危害；对……是有害的</t>
@@ -13064,6 +14144,16 @@
       <c r="A591" s="2" t="inlineStr">
         <is>
           <t>the food chain</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D591" s="2" t="inlineStr">
@@ -13169,6 +14259,16 @@
           <t>take part in</t>
         </is>
       </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 参加；贡献
@@ -13250,6 +14350,16 @@
           <t>pay for</t>
         </is>
       </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 付开销；赔偿(损失)；(为某种过失)付出代价；吃亏
@@ -13261,6 +14371,16 @@
       <c r="A601" s="2" t="inlineStr">
         <is>
           <t>take action</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D601" s="2" t="inlineStr">
@@ -13367,6 +14487,16 @@
           <t>put sth. to good use</t>
         </is>
       </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 施展；发挥；充分加以利用</t>
@@ -13377,6 +14507,16 @@
       <c r="A607" s="2" t="inlineStr">
         <is>
           <t>pull ... down</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D607" s="2" t="inlineStr">
@@ -13583,6 +14723,16 @@
           <t>bring back</t>
         </is>
       </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 送回；使恢复；使回忆起
@@ -13618,6 +14768,16 @@
           <t>WildAid</t>
         </is>
       </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D618" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 野生救援协会；野生动物救援协会；野生救援组织</t>
@@ -13630,6 +14790,16 @@
           <t>WWF</t>
         </is>
       </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D619" s="2" t="inlineStr">
         <is>
           <t>abbr. 世界自然基金会（World Wildlife Fund）；世界摔跤联合会（World Wrestling Federation）；雨天流量（Wet-Weather Flow）</t>
@@ -13640,6 +14810,16 @@
       <c r="A620" s="2" t="inlineStr">
         <is>
           <t>World Wide Fund for Nature</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D620" s="2" t="inlineStr">
@@ -13791,6 +14971,16 @@
       <c r="A627" s="2" t="inlineStr">
         <is>
           <t>in a row</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D627" s="2" t="inlineStr">
@@ -13924,6 +15114,16 @@
           <t>look back at</t>
         </is>
       </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D633" s="2" t="inlineStr">
         <is>
           <t>无</t>
@@ -13957,6 +15157,16 @@
       <c r="A635" s="2" t="inlineStr">
         <is>
           <t>make a mess</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D635" s="2" t="inlineStr">
@@ -13996,6 +15206,16 @@
           <t>keep one's cool</t>
         </is>
       </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D637" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">un. 保持冷静
@@ -14079,6 +15299,16 @@
           <t>senior high</t>
         </is>
       </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 〈美〉高级中学(10--12年级)
@@ -14092,6 +15322,16 @@
           <t>senior high school</t>
         </is>
       </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D642" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">n. （美国）高中
@@ -14126,6 +15366,16 @@
       <c r="A644" s="2" t="inlineStr">
         <is>
           <t>go by</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D644" s="2" t="inlineStr">
@@ -14211,6 +15461,16 @@
           <t>believe in</t>
         </is>
       </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D648" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">v. 相信
@@ -14290,6 +15550,16 @@
           <t>first of all</t>
         </is>
       </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D652" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 第一
@@ -14347,6 +15617,16 @@
           <t>be thirsty for</t>
         </is>
       </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D655" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 渴望；渴求；渴望得到</t>
@@ -14381,6 +15661,16 @@
           <t>be thankful to sb.</t>
         </is>
       </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D657" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> 感激；感谢；感激的</t>
@@ -14484,6 +15774,16 @@
           <t>along with</t>
         </is>
       </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D662" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">na. 与…一道；以外
@@ -14517,6 +15817,16 @@
       <c r="A664" s="2" t="inlineStr">
         <is>
           <t>be responsible for</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -14580,6 +15890,16 @@
           <t>separate from</t>
         </is>
       </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D667" s="2" t="inlineStr">
         <is>
           <t>把...和...分开, 把...和...区分开, 使...从...离析</t>
@@ -14659,6 +15979,16 @@
       <c r="A671" s="2" t="inlineStr">
         <is>
           <t>Griffin</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>无</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
